--- a/Data/CRMAccuracyData.xlsx
+++ b/Data/CRMAccuracyData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Titrator\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63CE21A9-BEA5-4614-A5AE-F76E0914976C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61334A7B-CC61-4144-8899-50A4605B449F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15330" yWindow="45" windowWidth="12975" windowHeight="15135" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13875" yWindow="0" windowWidth="14775" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CRMAccuracyData" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="128">
   <si>
     <t>Date</t>
   </si>
@@ -414,13 +414,16 @@
   </si>
   <si>
     <t>same CRM opened 08/27/2026, REDID</t>
+  </si>
+  <si>
+    <t>same CRM opened 08/27/2026, New pH probe</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -579,6 +582,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Lucida Console"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="34">
@@ -937,7 +946,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -947,6 +956,9 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1270,7 +1282,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G345"/>
+  <dimension ref="A1:G346"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -8340,6 +8352,27 @@
         <v>125</v>
       </c>
     </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A346" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B346" s="7">
+        <v>2201.1605500000001</v>
+      </c>
+      <c r="C346">
+        <v>2212.31</v>
+      </c>
+      <c r="D346">
+        <f>100*(B346-C346)/C346</f>
+        <v>-0.50397322255922039</v>
+      </c>
+      <c r="E346">
+        <v>217</v>
+      </c>
+      <c r="F346" t="s">
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/CRMAccuracyData.xlsx
+++ b/Data/CRMAccuracyData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Titrator\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61334A7B-CC61-4144-8899-50A4605B449F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB846E59-6434-4194-8F04-986B77735589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13875" yWindow="0" windowWidth="14775" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="720" windowWidth="14775" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CRMAccuracyData" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="128">
   <si>
     <t>Date</t>
   </si>
@@ -1282,7 +1282,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G346"/>
+  <dimension ref="A1:G347"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -8258,7 +8258,7 @@
         <v>2212.31</v>
       </c>
       <c r="D341">
-        <f>100*(B341-C341)/C341</f>
+        <f t="shared" ref="D341:D347" si="16">100*(B341-C341)/C341</f>
         <v>-5.0096505462621628E-2</v>
       </c>
       <c r="E341">
@@ -8279,7 +8279,7 @@
         <v>2212.31</v>
       </c>
       <c r="D342">
-        <f>100*(B342-C342)/C342</f>
+        <f t="shared" si="16"/>
         <v>0.45164782512396029</v>
       </c>
       <c r="E342">
@@ -8300,7 +8300,7 @@
         <v>2212.31</v>
       </c>
       <c r="D343">
-        <f>100*(B343-C343)/C343</f>
+        <f t="shared" si="16"/>
         <v>0.88534699025001196</v>
       </c>
       <c r="E343">
@@ -8321,7 +8321,7 @@
         <v>2212.31</v>
       </c>
       <c r="D344">
-        <f>100*(B344-C344)/C344</f>
+        <f t="shared" si="16"/>
         <v>0.38471507157676671</v>
       </c>
       <c r="E344">
@@ -8342,7 +8342,7 @@
         <v>2212.31</v>
       </c>
       <c r="D345">
-        <f>100*(B345-C345)/C345</f>
+        <f t="shared" si="16"/>
         <v>-5.1107665743038141E-2</v>
       </c>
       <c r="E345">
@@ -8363,7 +8363,7 @@
         <v>2212.31</v>
       </c>
       <c r="D346">
-        <f>100*(B346-C346)/C346</f>
+        <f t="shared" si="16"/>
         <v>-0.50397322255922039</v>
       </c>
       <c r="E346">
@@ -8371,6 +8371,27 @@
       </c>
       <c r="F346" t="s">
         <v>127</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A347" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B347" s="2">
+        <v>2209.8926799999999</v>
+      </c>
+      <c r="C347">
+        <v>2212.31</v>
+      </c>
+      <c r="D347">
+        <f t="shared" si="16"/>
+        <v>-0.10926678449222839</v>
+      </c>
+      <c r="E347">
+        <v>217</v>
+      </c>
+      <c r="F347" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/Data/CRMAccuracyData.xlsx
+++ b/Data/CRMAccuracyData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Titrator\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB846E59-6434-4194-8F04-986B77735589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4393DDEF-1B2E-46E8-89AC-869AB097CF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="720" windowWidth="14775" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13680" yWindow="510" windowWidth="14775" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CRMAccuracyData" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="128">
   <si>
     <t>Date</t>
   </si>
@@ -1282,7 +1282,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G347"/>
+  <dimension ref="A1:G348"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -8258,7 +8258,7 @@
         <v>2212.31</v>
       </c>
       <c r="D341">
-        <f t="shared" ref="D341:D347" si="16">100*(B341-C341)/C341</f>
+        <f t="shared" ref="D341:D348" si="16">100*(B341-C341)/C341</f>
         <v>-5.0096505462621628E-2</v>
       </c>
       <c r="E341">
@@ -8391,6 +8391,27 @@
         <v>217</v>
       </c>
       <c r="F347" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A348" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B348" s="2">
+        <v>2209.0641000000001</v>
+      </c>
+      <c r="C348">
+        <v>2212.31</v>
+      </c>
+      <c r="D348">
+        <f t="shared" si="16"/>
+        <v>-0.14671994431159704</v>
+      </c>
+      <c r="E348">
+        <v>217</v>
+      </c>
+      <c r="F348" t="s">
         <v>125</v>
       </c>
     </row>

--- a/Data/CRMAccuracyData.xlsx
+++ b/Data/CRMAccuracyData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Titrator\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4393DDEF-1B2E-46E8-89AC-869AB097CF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9840798C-3758-41C6-A1D3-2C44CCDD34EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13680" yWindow="510" windowWidth="14775" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13875" yWindow="0" windowWidth="14775" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CRMAccuracyData" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="129">
   <si>
     <t>Date</t>
   </si>
@@ -417,6 +417,9 @@
   </si>
   <si>
     <t>same CRM opened 08/27/2026, New pH probe</t>
+  </si>
+  <si>
+    <t>new CRM opened 9/18/2026</t>
   </si>
 </sst>
 </file>
@@ -1282,7 +1285,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G348"/>
+  <dimension ref="A1:G349"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -8258,7 +8261,7 @@
         <v>2212.31</v>
       </c>
       <c r="D341">
-        <f t="shared" ref="D341:D348" si="16">100*(B341-C341)/C341</f>
+        <f t="shared" ref="D341:D349" si="16">100*(B341-C341)/C341</f>
         <v>-5.0096505462621628E-2</v>
       </c>
       <c r="E341">
@@ -8413,6 +8416,27 @@
       </c>
       <c r="F348" t="s">
         <v>125</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A349" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B349" s="2">
+        <v>2207.9616700000001</v>
+      </c>
+      <c r="C349">
+        <v>2212.31</v>
+      </c>
+      <c r="D349">
+        <f t="shared" si="16"/>
+        <v>-0.19655156827026074</v>
+      </c>
+      <c r="E349">
+        <v>217</v>
+      </c>
+      <c r="F349" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/Data/CRMAccuracyData.xlsx
+++ b/Data/CRMAccuracyData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Titrator\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9840798C-3758-41C6-A1D3-2C44CCDD34EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE2B8BC-6CA8-499C-A3E4-CA1E8C79A17B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13875" yWindow="0" windowWidth="14775" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8423,14 +8423,14 @@
         <v>46283</v>
       </c>
       <c r="B349" s="2">
-        <v>2207.9616700000001</v>
+        <v>2209.1144800000002</v>
       </c>
       <c r="C349">
         <v>2212.31</v>
       </c>
       <c r="D349">
         <f t="shared" si="16"/>
-        <v>-0.19655156827026074</v>
+        <v>-0.1444426866035845</v>
       </c>
       <c r="E349">
         <v>217</v>

--- a/Data/CRMAccuracyData.xlsx
+++ b/Data/CRMAccuracyData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Titrator\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE2B8BC-6CA8-499C-A3E4-CA1E8C79A17B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71EB93F7-2DC0-408A-B825-E404307912BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13875" yWindow="0" windowWidth="14775" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="130">
   <si>
     <t>Date</t>
   </si>
@@ -420,6 +420,9 @@
   </si>
   <si>
     <t>new CRM opened 9/18/2026</t>
+  </si>
+  <si>
+    <t>same CRM opened 9/18/2026</t>
   </si>
 </sst>
 </file>
@@ -1285,7 +1288,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G349"/>
+  <dimension ref="A1:G350"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -8261,7 +8264,7 @@
         <v>2212.31</v>
       </c>
       <c r="D341">
-        <f t="shared" ref="D341:D349" si="16">100*(B341-C341)/C341</f>
+        <f t="shared" ref="D341:D350" si="16">100*(B341-C341)/C341</f>
         <v>-5.0096505462621628E-2</v>
       </c>
       <c r="E341">
@@ -8437,6 +8440,27 @@
       </c>
       <c r="F349" t="s">
         <v>128</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A350" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B350" s="2">
+        <v>2213.4127100000001</v>
+      </c>
+      <c r="C350">
+        <v>2212.31</v>
+      </c>
+      <c r="D350">
+        <f t="shared" si="16"/>
+        <v>4.9844280412786435E-2</v>
+      </c>
+      <c r="E350">
+        <v>217</v>
+      </c>
+      <c r="F350" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/Data/CRMAccuracyData.xlsx
+++ b/Data/CRMAccuracyData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Titrator\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71EB93F7-2DC0-408A-B825-E404307912BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE790A2A-A0E8-4AB9-8FE8-8D946BA43E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13875" yWindow="0" windowWidth="14775" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="720" windowWidth="14775" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CRMAccuracyData" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="130">
   <si>
     <t>Date</t>
   </si>
@@ -1288,7 +1288,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G350"/>
+  <dimension ref="A1:G351"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -8264,7 +8264,7 @@
         <v>2212.31</v>
       </c>
       <c r="D341">
-        <f t="shared" ref="D341:D350" si="16">100*(B341-C341)/C341</f>
+        <f t="shared" ref="D341:D351" si="16">100*(B341-C341)/C341</f>
         <v>-5.0096505462621628E-2</v>
       </c>
       <c r="E341">
@@ -8460,6 +8460,27 @@
         <v>217</v>
       </c>
       <c r="F350" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A351" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B351" s="2">
+        <v>2217.68084</v>
+      </c>
+      <c r="C351">
+        <v>2212.31</v>
+      </c>
+      <c r="D351">
+        <f t="shared" si="16"/>
+        <v>0.24277067861195059</v>
+      </c>
+      <c r="E351">
+        <v>217</v>
+      </c>
+      <c r="F351" t="s">
         <v>129</v>
       </c>
     </row>

--- a/Data/CRMAccuracyData.xlsx
+++ b/Data/CRMAccuracyData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Titrator\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE790A2A-A0E8-4AB9-8FE8-8D946BA43E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7048727F-B9B9-4909-9FF6-717C1F0B0088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="720" windowWidth="14775" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13965" yWindow="0" windowWidth="14775" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CRMAccuracyData" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="131">
   <si>
     <t>Date</t>
   </si>
@@ -423,6 +423,9 @@
   </si>
   <si>
     <t>same CRM opened 9/18/2026</t>
+  </si>
+  <si>
+    <t>same CRM opened 9/18/2026, MP ran at end of 62 samples</t>
   </si>
 </sst>
 </file>
@@ -1288,7 +1291,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G351"/>
+  <dimension ref="A1:G353"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -8264,7 +8267,7 @@
         <v>2212.31</v>
       </c>
       <c r="D341">
-        <f t="shared" ref="D341:D351" si="16">100*(B341-C341)/C341</f>
+        <f t="shared" ref="D341:D353" si="16">100*(B341-C341)/C341</f>
         <v>-5.0096505462621628E-2</v>
       </c>
       <c r="E341">
@@ -8482,6 +8485,48 @@
       </c>
       <c r="F351" t="s">
         <v>129</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A352" s="1">
+        <v>46314</v>
+      </c>
+      <c r="B352" s="2">
+        <v>2209.7436200000002</v>
+      </c>
+      <c r="C352">
+        <v>2212.31</v>
+      </c>
+      <c r="D352">
+        <f t="shared" si="16"/>
+        <v>-0.11600453824282102</v>
+      </c>
+      <c r="E352">
+        <v>217</v>
+      </c>
+      <c r="F352" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A353" s="1">
+        <v>46314</v>
+      </c>
+      <c r="B353" s="2">
+        <v>2213.4907400000002</v>
+      </c>
+      <c r="C353">
+        <v>2212.31</v>
+      </c>
+      <c r="D353">
+        <f t="shared" si="16"/>
+        <v>5.3371362964514092E-2</v>
+      </c>
+      <c r="E353">
+        <v>217</v>
+      </c>
+      <c r="F353" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/Data/CRMAccuracyData.xlsx
+++ b/Data/CRMAccuracyData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Titrator\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7048727F-B9B9-4909-9FF6-717C1F0B0088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2220BA3B-D8EB-4B49-A72D-74CDE7A305C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13965" yWindow="0" windowWidth="14775" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="131">
   <si>
     <t>Date</t>
   </si>
@@ -1291,7 +1291,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G353"/>
+  <dimension ref="A1:G354"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -8267,7 +8267,7 @@
         <v>2212.31</v>
       </c>
       <c r="D341">
-        <f t="shared" ref="D341:D353" si="16">100*(B341-C341)/C341</f>
+        <f t="shared" ref="D341:D354" si="16">100*(B341-C341)/C341</f>
         <v>-5.0096505462621628E-2</v>
       </c>
       <c r="E341">
@@ -8527,6 +8527,27 @@
       </c>
       <c r="F353" t="s">
         <v>130</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A354" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B354" s="2">
+        <v>2209.8549499999999</v>
+      </c>
+      <c r="C354">
+        <v>2212.31</v>
+      </c>
+      <c r="D354">
+        <f t="shared" si="16"/>
+        <v>-0.11097224168403291</v>
+      </c>
+      <c r="E354">
+        <v>217</v>
+      </c>
+      <c r="F354" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/Data/CRMAccuracyData.xlsx
+++ b/Data/CRMAccuracyData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Titrator\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2220BA3B-D8EB-4B49-A72D-74CDE7A305C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D2C5D31-A81C-4CA6-B3C6-AFB3244975D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13965" yWindow="0" windowWidth="14775" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13605" yWindow="690" windowWidth="14775" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CRMAccuracyData" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="131">
   <si>
     <t>Date</t>
   </si>
@@ -71,9 +71,6 @@
     <t>New CRM bottle (opened 02/14)</t>
   </si>
   <si>
-    <t>2/19/12019</t>
-  </si>
-  <si>
     <t>New CRM bottle (opened 02/19)</t>
   </si>
   <si>
@@ -426,6 +423,9 @@
   </si>
   <si>
     <t>same CRM opened 9/18/2026, MP ran at end of 62 samples</t>
+  </si>
+  <si>
+    <t>same CRM opened 9/18/2026 - testing Metrohm acid</t>
   </si>
 </sst>
 </file>
@@ -1291,7 +1291,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G354"/>
+  <dimension ref="A1:G356"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -1936,8 +1936,8 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>12</v>
+      <c r="A33" s="1">
+        <v>43515</v>
       </c>
       <c r="B33">
         <v>2226.3739999999998</v>
@@ -1952,7 +1952,7 @@
         <v>169</v>
       </c>
       <c r="F33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1972,7 +1972,7 @@
         <v>169</v>
       </c>
       <c r="F34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1992,7 +1992,7 @@
         <v>169</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2012,7 +2012,7 @@
         <v>169</v>
       </c>
       <c r="F36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2032,7 +2032,7 @@
         <v>169</v>
       </c>
       <c r="F37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2052,7 +2052,7 @@
         <v>169</v>
       </c>
       <c r="F38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2072,7 +2072,7 @@
         <v>169</v>
       </c>
       <c r="F39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2092,7 +2092,7 @@
         <v>169</v>
       </c>
       <c r="F40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2112,7 +2112,7 @@
         <v>169</v>
       </c>
       <c r="F41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2132,7 +2132,7 @@
         <v>169</v>
       </c>
       <c r="F42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2152,7 +2152,7 @@
         <v>169</v>
       </c>
       <c r="F43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2172,7 +2172,7 @@
         <v>169</v>
       </c>
       <c r="F44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2192,7 +2192,7 @@
         <v>169</v>
       </c>
       <c r="F45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2212,7 +2212,7 @@
         <v>169</v>
       </c>
       <c r="F46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2232,7 +2232,7 @@
         <v>169</v>
       </c>
       <c r="F47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2252,7 +2252,7 @@
         <v>169</v>
       </c>
       <c r="F48" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2272,7 +2272,7 @@
         <v>169</v>
       </c>
       <c r="F49" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2292,7 +2292,7 @@
         <v>169</v>
       </c>
       <c r="F50" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2312,7 +2312,7 @@
         <v>169</v>
       </c>
       <c r="F51" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2332,7 +2332,7 @@
         <v>169</v>
       </c>
       <c r="F52" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2352,7 +2352,7 @@
         <v>169</v>
       </c>
       <c r="F53" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2372,7 +2372,7 @@
         <v>169</v>
       </c>
       <c r="F54" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2392,7 +2392,7 @@
         <v>169</v>
       </c>
       <c r="F55" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2412,7 +2412,7 @@
         <v>169</v>
       </c>
       <c r="F56" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2432,7 +2432,7 @@
         <v>169</v>
       </c>
       <c r="F57" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2452,7 +2452,7 @@
         <v>169</v>
       </c>
       <c r="F58" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2472,7 +2472,7 @@
         <v>169</v>
       </c>
       <c r="F59" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2492,7 +2492,7 @@
         <v>169</v>
       </c>
       <c r="F60" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2512,7 +2512,7 @@
         <v>169</v>
       </c>
       <c r="F61" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2532,7 +2532,7 @@
         <v>169</v>
       </c>
       <c r="F62" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2552,7 +2552,7 @@
         <v>169</v>
       </c>
       <c r="F63" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2572,7 +2572,7 @@
         <v>169</v>
       </c>
       <c r="F64" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -2592,7 +2592,7 @@
         <v>169</v>
       </c>
       <c r="F65" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -2612,7 +2612,7 @@
         <v>169</v>
       </c>
       <c r="F66" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G66">
         <v>2208.879281</v>
@@ -2635,7 +2635,7 @@
         <v>169</v>
       </c>
       <c r="F67" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -2655,7 +2655,7 @@
         <v>169</v>
       </c>
       <c r="F68" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -2675,7 +2675,7 @@
         <v>169</v>
       </c>
       <c r="F69" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -2695,7 +2695,7 @@
         <v>169</v>
       </c>
       <c r="F70" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -2715,7 +2715,7 @@
         <v>169</v>
       </c>
       <c r="F71" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -2735,7 +2735,7 @@
         <v>169</v>
       </c>
       <c r="F72" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -2755,7 +2755,7 @@
         <v>169</v>
       </c>
       <c r="F73" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -2775,7 +2775,7 @@
         <v>169</v>
       </c>
       <c r="F74" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -2795,7 +2795,7 @@
         <v>169</v>
       </c>
       <c r="F75" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -2815,7 +2815,7 @@
         <v>169</v>
       </c>
       <c r="F76" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -2835,7 +2835,7 @@
         <v>169</v>
       </c>
       <c r="F77" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -2855,7 +2855,7 @@
         <v>169</v>
       </c>
       <c r="F78" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -2875,7 +2875,7 @@
         <v>169</v>
       </c>
       <c r="F79" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -2895,7 +2895,7 @@
         <v>169</v>
       </c>
       <c r="F80" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -2915,7 +2915,7 @@
         <v>169</v>
       </c>
       <c r="F81" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -2935,7 +2935,7 @@
         <v>169</v>
       </c>
       <c r="F82" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -2955,7 +2955,7 @@
         <v>169</v>
       </c>
       <c r="F83" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -2975,7 +2975,7 @@
         <v>169</v>
       </c>
       <c r="F84" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -2995,7 +2995,7 @@
         <v>169</v>
       </c>
       <c r="F85" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3015,7 +3015,7 @@
         <v>169</v>
       </c>
       <c r="F86" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3035,7 +3035,7 @@
         <v>169</v>
       </c>
       <c r="F87" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3055,7 +3055,7 @@
         <v>155</v>
       </c>
       <c r="F88" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3075,7 +3075,7 @@
         <v>155</v>
       </c>
       <c r="F89" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3095,7 +3095,7 @@
         <v>155</v>
       </c>
       <c r="F90" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3115,7 +3115,7 @@
         <v>155</v>
       </c>
       <c r="F91" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3135,7 +3135,7 @@
         <v>155</v>
       </c>
       <c r="F92" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3155,7 +3155,7 @@
         <v>155</v>
       </c>
       <c r="F93" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3175,7 +3175,7 @@
         <v>155</v>
       </c>
       <c r="F94" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3195,7 +3195,7 @@
         <v>169</v>
       </c>
       <c r="F95" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3215,7 +3215,7 @@
         <v>169</v>
       </c>
       <c r="F96" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -3235,7 +3235,7 @@
         <v>169</v>
       </c>
       <c r="F97" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -3255,7 +3255,7 @@
         <v>180</v>
       </c>
       <c r="F98" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -3275,7 +3275,7 @@
         <v>180</v>
       </c>
       <c r="F99" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -3295,7 +3295,7 @@
         <v>180</v>
       </c>
       <c r="F100" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -3315,7 +3315,7 @@
         <v>180</v>
       </c>
       <c r="F101" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -3335,10 +3335,10 @@
         <v>180</v>
       </c>
       <c r="F102" t="s">
+        <v>47</v>
+      </c>
+      <c r="G102" t="s">
         <v>48</v>
-      </c>
-      <c r="G102" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -3358,7 +3358,7 @@
         <v>180</v>
       </c>
       <c r="F103" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -3378,7 +3378,7 @@
         <v>180</v>
       </c>
       <c r="F104" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -3398,7 +3398,7 @@
         <v>180</v>
       </c>
       <c r="F105" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -3418,7 +3418,7 @@
         <v>180</v>
       </c>
       <c r="F106" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -3438,7 +3438,7 @@
         <v>180</v>
       </c>
       <c r="F107" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -3458,7 +3458,7 @@
         <v>183</v>
       </c>
       <c r="F108" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -3478,7 +3478,7 @@
         <v>183</v>
       </c>
       <c r="F109" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -3498,7 +3498,7 @@
         <v>183</v>
       </c>
       <c r="F110" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -3518,7 +3518,7 @@
         <v>183</v>
       </c>
       <c r="F111" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -3538,7 +3538,7 @@
         <v>183</v>
       </c>
       <c r="F112" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3558,7 +3558,7 @@
         <v>183</v>
       </c>
       <c r="F113" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3578,7 +3578,7 @@
         <v>183</v>
       </c>
       <c r="F114" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3598,7 +3598,7 @@
         <v>183</v>
       </c>
       <c r="F115" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3618,7 +3618,7 @@
         <v>183</v>
       </c>
       <c r="F116" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3638,7 +3638,7 @@
         <v>180</v>
       </c>
       <c r="F117" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3658,7 +3658,7 @@
         <v>183</v>
       </c>
       <c r="F118" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3678,7 +3678,7 @@
         <v>183</v>
       </c>
       <c r="F119" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3698,7 +3698,7 @@
         <v>183</v>
       </c>
       <c r="F120" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3718,7 +3718,7 @@
         <v>183</v>
       </c>
       <c r="F121" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -3738,7 +3738,7 @@
         <v>191</v>
       </c>
       <c r="F122" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3758,7 +3758,7 @@
         <v>183</v>
       </c>
       <c r="F123" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3778,7 +3778,7 @@
         <v>191</v>
       </c>
       <c r="F124" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3798,7 +3798,7 @@
         <v>191</v>
       </c>
       <c r="F125" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -3818,7 +3818,7 @@
         <v>180</v>
       </c>
       <c r="F126" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -3838,7 +3838,7 @@
         <v>180</v>
       </c>
       <c r="F127" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -3858,7 +3858,7 @@
         <v>180</v>
       </c>
       <c r="F128" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -3878,7 +3878,7 @@
         <v>180</v>
       </c>
       <c r="F129" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -3898,7 +3898,7 @@
         <v>180</v>
       </c>
       <c r="F130" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -3918,7 +3918,7 @@
         <v>180</v>
       </c>
       <c r="F131" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -3938,7 +3938,7 @@
         <v>180</v>
       </c>
       <c r="F132" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -3958,7 +3958,7 @@
         <v>180</v>
       </c>
       <c r="F133" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -3978,7 +3978,7 @@
         <v>180</v>
       </c>
       <c r="F134" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -3998,7 +3998,7 @@
         <v>183</v>
       </c>
       <c r="F135" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4018,7 +4018,7 @@
         <v>183</v>
       </c>
       <c r="F136" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4038,7 +4038,7 @@
         <v>183</v>
       </c>
       <c r="F137" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4058,7 +4058,7 @@
         <v>191</v>
       </c>
       <c r="F138" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4078,7 +4078,7 @@
         <v>191</v>
       </c>
       <c r="F139" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4098,7 +4098,7 @@
         <v>191</v>
       </c>
       <c r="F140" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4118,7 +4118,7 @@
         <v>180</v>
       </c>
       <c r="F141" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4155,7 +4155,7 @@
         <v>180</v>
       </c>
       <c r="F143" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4175,7 +4175,7 @@
         <v>183</v>
       </c>
       <c r="F144" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4195,7 +4195,7 @@
         <v>183</v>
       </c>
       <c r="F145" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4215,7 +4215,7 @@
         <v>183</v>
       </c>
       <c r="F146" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4235,7 +4235,7 @@
         <v>191</v>
       </c>
       <c r="F147" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4255,7 +4255,7 @@
         <v>191</v>
       </c>
       <c r="F148" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4275,7 +4275,7 @@
         <v>191</v>
       </c>
       <c r="F149" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4295,7 +4295,7 @@
         <v>191</v>
       </c>
       <c r="F150" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -4315,7 +4315,7 @@
         <v>191</v>
       </c>
       <c r="F151" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4335,7 +4335,7 @@
         <v>191</v>
       </c>
       <c r="F152" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4355,7 +4355,7 @@
         <v>191</v>
       </c>
       <c r="F153" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -4375,7 +4375,7 @@
         <v>191</v>
       </c>
       <c r="F154" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -4395,7 +4395,7 @@
         <v>191</v>
       </c>
       <c r="F155" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4415,7 +4415,7 @@
         <v>191</v>
       </c>
       <c r="F156" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4435,7 +4435,7 @@
         <v>191</v>
       </c>
       <c r="F157" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -4455,7 +4455,7 @@
         <v>191</v>
       </c>
       <c r="F158" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -4475,7 +4475,7 @@
         <v>191</v>
       </c>
       <c r="F159" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4495,7 +4495,7 @@
         <v>191</v>
       </c>
       <c r="F160" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4515,7 +4515,7 @@
         <v>202</v>
       </c>
       <c r="F161" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4535,7 +4535,7 @@
         <v>202</v>
       </c>
       <c r="F162" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4555,7 +4555,7 @@
         <v>207</v>
       </c>
       <c r="F163" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -4575,7 +4575,7 @@
         <v>207</v>
       </c>
       <c r="F164" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -4595,7 +4595,7 @@
         <v>207</v>
       </c>
       <c r="F165" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -4615,7 +4615,7 @@
         <v>207</v>
       </c>
       <c r="F166" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -4636,7 +4636,7 @@
         <v>207</v>
       </c>
       <c r="F167" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -4693,7 +4693,7 @@
         <v>207</v>
       </c>
       <c r="F170" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -4714,7 +4714,7 @@
         <v>207</v>
       </c>
       <c r="F171" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -4735,7 +4735,7 @@
         <v>207</v>
       </c>
       <c r="F172" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -4756,7 +4756,7 @@
         <v>207</v>
       </c>
       <c r="F173" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -4777,7 +4777,7 @@
         <v>207</v>
       </c>
       <c r="F174" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -4798,7 +4798,7 @@
         <v>207</v>
       </c>
       <c r="F175" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -4819,7 +4819,7 @@
         <v>207</v>
       </c>
       <c r="F176" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -4840,7 +4840,7 @@
         <v>207</v>
       </c>
       <c r="F177" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -4861,7 +4861,7 @@
         <v>207</v>
       </c>
       <c r="F178" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -4882,7 +4882,7 @@
         <v>207</v>
       </c>
       <c r="F179" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -4903,7 +4903,7 @@
         <v>207</v>
       </c>
       <c r="F180" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -4924,7 +4924,7 @@
         <v>207</v>
       </c>
       <c r="F181" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -4945,7 +4945,7 @@
         <v>207</v>
       </c>
       <c r="F182" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -4966,7 +4966,7 @@
         <v>202</v>
       </c>
       <c r="F183" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -4987,7 +4987,7 @@
         <v>202</v>
       </c>
       <c r="F184" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -5008,7 +5008,7 @@
         <v>202</v>
       </c>
       <c r="F185" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -5029,7 +5029,7 @@
         <v>202</v>
       </c>
       <c r="F186" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -5050,7 +5050,7 @@
         <v>202</v>
       </c>
       <c r="F187" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -5071,7 +5071,7 @@
         <v>202</v>
       </c>
       <c r="F188" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -5092,7 +5092,7 @@
         <v>202</v>
       </c>
       <c r="F189" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -5113,7 +5113,7 @@
         <v>202</v>
       </c>
       <c r="F190" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -5134,7 +5134,7 @@
         <v>202</v>
       </c>
       <c r="F191" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -5155,7 +5155,7 @@
         <v>202</v>
       </c>
       <c r="F192" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -5176,7 +5176,7 @@
         <v>202</v>
       </c>
       <c r="F193" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -5197,7 +5197,7 @@
         <v>202</v>
       </c>
       <c r="F194" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -5218,7 +5218,7 @@
         <v>202</v>
       </c>
       <c r="F195" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -5239,7 +5239,7 @@
         <v>202</v>
       </c>
       <c r="F196" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -5260,7 +5260,7 @@
         <v>202</v>
       </c>
       <c r="F197" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -5281,7 +5281,7 @@
         <v>202</v>
       </c>
       <c r="F198" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -5302,7 +5302,7 @@
         <v>202</v>
       </c>
       <c r="F199" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -5323,7 +5323,7 @@
         <v>202</v>
       </c>
       <c r="F200" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -5344,7 +5344,7 @@
         <v>202</v>
       </c>
       <c r="F201" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -5365,7 +5365,7 @@
         <v>183</v>
       </c>
       <c r="F202" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -5386,7 +5386,7 @@
         <v>210</v>
       </c>
       <c r="F203" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -5407,7 +5407,7 @@
         <v>210</v>
       </c>
       <c r="F204" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -5428,7 +5428,7 @@
         <v>210</v>
       </c>
       <c r="F205" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -5449,7 +5449,7 @@
         <v>210</v>
       </c>
       <c r="F206" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -5470,7 +5470,7 @@
         <v>210</v>
       </c>
       <c r="F207" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -5491,7 +5491,7 @@
         <v>210</v>
       </c>
       <c r="F208" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -5512,7 +5512,7 @@
         <v>210</v>
       </c>
       <c r="F209" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -5533,7 +5533,7 @@
         <v>210</v>
       </c>
       <c r="F210" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -5554,7 +5554,7 @@
         <v>210</v>
       </c>
       <c r="F211" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -5575,7 +5575,7 @@
         <v>210</v>
       </c>
       <c r="F212" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -5596,7 +5596,7 @@
         <v>210</v>
       </c>
       <c r="F213" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -5617,7 +5617,7 @@
         <v>210</v>
       </c>
       <c r="F214" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -5638,7 +5638,7 @@
         <v>210</v>
       </c>
       <c r="F215" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -5659,7 +5659,7 @@
         <v>210</v>
       </c>
       <c r="F216" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -5680,7 +5680,7 @@
         <v>210</v>
       </c>
       <c r="F217" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -5692,7 +5692,7 @@
         <v>-100</v>
       </c>
       <c r="F218" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -5713,7 +5713,7 @@
         <v>210</v>
       </c>
       <c r="F219" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -5734,7 +5734,7 @@
         <v>210</v>
       </c>
       <c r="F220" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -5755,7 +5755,7 @@
         <v>210</v>
       </c>
       <c r="F221" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -5776,7 +5776,7 @@
         <v>210</v>
       </c>
       <c r="F222" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -5797,7 +5797,7 @@
         <v>210</v>
       </c>
       <c r="F223" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -5818,7 +5818,7 @@
         <v>169</v>
       </c>
       <c r="F224" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -5839,7 +5839,7 @@
         <v>169</v>
       </c>
       <c r="F225" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -5860,7 +5860,7 @@
         <v>169</v>
       </c>
       <c r="F226" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -5881,7 +5881,7 @@
         <v>169</v>
       </c>
       <c r="F227" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -5902,7 +5902,7 @@
         <v>169</v>
       </c>
       <c r="F228" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -5923,7 +5923,7 @@
         <v>212</v>
       </c>
       <c r="F229" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -5944,7 +5944,7 @@
         <v>212</v>
       </c>
       <c r="F230" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -5965,7 +5965,7 @@
         <v>212</v>
       </c>
       <c r="F231" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -5986,7 +5986,7 @@
         <v>212</v>
       </c>
       <c r="F232" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -6007,7 +6007,7 @@
         <v>212</v>
       </c>
       <c r="F233" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -6028,7 +6028,7 @@
         <v>212</v>
       </c>
       <c r="F234" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -6049,7 +6049,7 @@
         <v>183</v>
       </c>
       <c r="F235" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -6070,7 +6070,7 @@
         <v>183</v>
       </c>
       <c r="F236" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -6091,7 +6091,7 @@
         <v>183</v>
       </c>
       <c r="F237" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -6112,7 +6112,7 @@
         <v>183</v>
       </c>
       <c r="F238" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -6133,7 +6133,7 @@
         <v>183</v>
       </c>
       <c r="F239" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -6154,7 +6154,7 @@
         <v>202</v>
       </c>
       <c r="F240" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -6174,7 +6174,7 @@
         <v>202</v>
       </c>
       <c r="F241" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -6195,7 +6195,7 @@
         <v>202</v>
       </c>
       <c r="F242" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -6216,7 +6216,7 @@
         <v>202</v>
       </c>
       <c r="F243" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -6237,7 +6237,7 @@
         <v>202</v>
       </c>
       <c r="F244" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -6258,7 +6258,7 @@
         <v>202</v>
       </c>
       <c r="F245" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -6279,7 +6279,7 @@
         <v>202</v>
       </c>
       <c r="F246" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -6300,7 +6300,7 @@
         <v>202</v>
       </c>
       <c r="F247" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -6321,7 +6321,7 @@
         <v>202</v>
       </c>
       <c r="F248" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -6342,7 +6342,7 @@
         <v>183</v>
       </c>
       <c r="F249" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -6363,7 +6363,7 @@
         <v>183</v>
       </c>
       <c r="F250" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -6384,7 +6384,7 @@
         <v>183</v>
       </c>
       <c r="F251" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -6405,7 +6405,7 @@
         <v>183</v>
       </c>
       <c r="F252" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -6426,7 +6426,7 @@
         <v>183</v>
       </c>
       <c r="F253" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -6447,7 +6447,7 @@
         <v>210</v>
       </c>
       <c r="F254" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -6468,7 +6468,7 @@
         <v>210</v>
       </c>
       <c r="F255" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -6489,7 +6489,7 @@
         <v>210</v>
       </c>
       <c r="F256" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -6510,7 +6510,7 @@
         <v>210</v>
       </c>
       <c r="F257" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -6531,7 +6531,7 @@
         <v>210</v>
       </c>
       <c r="F258" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -6552,7 +6552,7 @@
         <v>210</v>
       </c>
       <c r="F259" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -6573,7 +6573,7 @@
         <v>210</v>
       </c>
       <c r="F260" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -6594,7 +6594,7 @@
         <v>210</v>
       </c>
       <c r="F261" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -6615,7 +6615,7 @@
         <v>180</v>
       </c>
       <c r="F262" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -6636,7 +6636,7 @@
         <v>180</v>
       </c>
       <c r="F263" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -6657,7 +6657,7 @@
         <v>180</v>
       </c>
       <c r="F264" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -6678,7 +6678,7 @@
         <v>180</v>
       </c>
       <c r="F265" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -6699,7 +6699,7 @@
         <v>180</v>
       </c>
       <c r="F266" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -6720,7 +6720,7 @@
         <v>217</v>
       </c>
       <c r="F267" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -6741,7 +6741,7 @@
         <v>217</v>
       </c>
       <c r="F268" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -6762,7 +6762,7 @@
         <v>217</v>
       </c>
       <c r="F269" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -6783,7 +6783,7 @@
         <v>217</v>
       </c>
       <c r="F270" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -6804,7 +6804,7 @@
         <v>217</v>
       </c>
       <c r="F271" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -6825,7 +6825,7 @@
         <v>217</v>
       </c>
       <c r="F272" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -6846,7 +6846,7 @@
         <v>217</v>
       </c>
       <c r="F273" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -6867,7 +6867,7 @@
         <v>217</v>
       </c>
       <c r="F274" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -6888,7 +6888,7 @@
         <v>217</v>
       </c>
       <c r="F275" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -6909,7 +6909,7 @@
         <v>217</v>
       </c>
       <c r="F276" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -6930,7 +6930,7 @@
         <v>217</v>
       </c>
       <c r="F277" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -6951,7 +6951,7 @@
         <v>217</v>
       </c>
       <c r="F278" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -6972,7 +6972,7 @@
         <v>217</v>
       </c>
       <c r="F279" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -6993,7 +6993,7 @@
         <v>217</v>
       </c>
       <c r="F280" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -7014,7 +7014,7 @@
         <v>217</v>
       </c>
       <c r="F281" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -7035,7 +7035,7 @@
         <v>217</v>
       </c>
       <c r="F282" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -7056,7 +7056,7 @@
         <v>217</v>
       </c>
       <c r="F283" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -7077,7 +7077,7 @@
         <v>217</v>
       </c>
       <c r="F284" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -7098,7 +7098,7 @@
         <v>217</v>
       </c>
       <c r="F285" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -7119,7 +7119,7 @@
         <v>217</v>
       </c>
       <c r="F286" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -7140,7 +7140,7 @@
         <v>217</v>
       </c>
       <c r="F287" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -7161,7 +7161,7 @@
         <v>217</v>
       </c>
       <c r="F288" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -7182,7 +7182,7 @@
         <v>217</v>
       </c>
       <c r="F289" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -7203,7 +7203,7 @@
         <v>217</v>
       </c>
       <c r="F290" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -7224,7 +7224,7 @@
         <v>217</v>
       </c>
       <c r="F291" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -7245,7 +7245,7 @@
         <v>217</v>
       </c>
       <c r="F292" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -7266,7 +7266,7 @@
         <v>217</v>
       </c>
       <c r="F293" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -7287,7 +7287,7 @@
         <v>217</v>
       </c>
       <c r="F294" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -7308,7 +7308,7 @@
         <v>217</v>
       </c>
       <c r="F295" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -7329,7 +7329,7 @@
         <v>217</v>
       </c>
       <c r="F296" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -7350,7 +7350,7 @@
         <v>217</v>
       </c>
       <c r="F297" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -7371,7 +7371,7 @@
         <v>217</v>
       </c>
       <c r="F298" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -7392,7 +7392,7 @@
         <v>217</v>
       </c>
       <c r="F299" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -7413,7 +7413,7 @@
         <v>217</v>
       </c>
       <c r="F300" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -7434,7 +7434,7 @@
         <v>217</v>
       </c>
       <c r="F301" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -7455,7 +7455,7 @@
         <v>217</v>
       </c>
       <c r="F302" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
@@ -7476,7 +7476,7 @@
         <v>217</v>
       </c>
       <c r="F303" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -7497,7 +7497,7 @@
         <v>217</v>
       </c>
       <c r="F304" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -7518,7 +7518,7 @@
         <v>217</v>
       </c>
       <c r="F305" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -7539,7 +7539,7 @@
         <v>217</v>
       </c>
       <c r="F306" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -7560,7 +7560,7 @@
         <v>217</v>
       </c>
       <c r="F307" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -7581,7 +7581,7 @@
         <v>217</v>
       </c>
       <c r="F308" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -7602,7 +7602,7 @@
         <v>217</v>
       </c>
       <c r="F309" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -7623,7 +7623,7 @@
         <v>217</v>
       </c>
       <c r="F310" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -7644,7 +7644,7 @@
         <v>217</v>
       </c>
       <c r="F311" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
@@ -7665,7 +7665,7 @@
         <v>217</v>
       </c>
       <c r="F312" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -7686,7 +7686,7 @@
         <v>217</v>
       </c>
       <c r="F313" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -7707,7 +7707,7 @@
         <v>217</v>
       </c>
       <c r="F314" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -7728,7 +7728,7 @@
         <v>217</v>
       </c>
       <c r="F315" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -7749,7 +7749,7 @@
         <v>217</v>
       </c>
       <c r="F316" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -7770,7 +7770,7 @@
         <v>217</v>
       </c>
       <c r="F317" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -7791,7 +7791,7 @@
         <v>217</v>
       </c>
       <c r="F318" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -7812,7 +7812,7 @@
         <v>217</v>
       </c>
       <c r="F319" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -7833,7 +7833,7 @@
         <v>217</v>
       </c>
       <c r="F320" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -7854,7 +7854,7 @@
         <v>217</v>
       </c>
       <c r="F321" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -7875,7 +7875,7 @@
         <v>217</v>
       </c>
       <c r="F322" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -7896,7 +7896,7 @@
         <v>217</v>
       </c>
       <c r="F323" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -7917,7 +7917,7 @@
         <v>217</v>
       </c>
       <c r="F324" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -7938,7 +7938,7 @@
         <v>217</v>
       </c>
       <c r="F325" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -7959,7 +7959,7 @@
         <v>217</v>
       </c>
       <c r="F326" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -7980,7 +7980,7 @@
         <v>217</v>
       </c>
       <c r="F327" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -8001,7 +8001,7 @@
         <v>217</v>
       </c>
       <c r="F328" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -8022,7 +8022,7 @@
         <v>217</v>
       </c>
       <c r="F329" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -8043,7 +8043,7 @@
         <v>217</v>
       </c>
       <c r="F330" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -8064,7 +8064,7 @@
         <v>217</v>
       </c>
       <c r="F331" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -8085,7 +8085,7 @@
         <v>217</v>
       </c>
       <c r="F332" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -8106,7 +8106,7 @@
         <v>217</v>
       </c>
       <c r="F333" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -8127,7 +8127,7 @@
         <v>217</v>
       </c>
       <c r="F334" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -8148,7 +8148,7 @@
         <v>217</v>
       </c>
       <c r="F335" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -8169,7 +8169,7 @@
         <v>217</v>
       </c>
       <c r="F336" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -8190,7 +8190,7 @@
         <v>217</v>
       </c>
       <c r="F337" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -8211,7 +8211,7 @@
         <v>217</v>
       </c>
       <c r="F338" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -8232,7 +8232,7 @@
         <v>217</v>
       </c>
       <c r="F339" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -8253,7 +8253,7 @@
         <v>217</v>
       </c>
       <c r="F340" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -8267,14 +8267,14 @@
         <v>2212.31</v>
       </c>
       <c r="D341">
-        <f t="shared" ref="D341:D354" si="16">100*(B341-C341)/C341</f>
+        <f t="shared" ref="D341:D356" si="16">100*(B341-C341)/C341</f>
         <v>-5.0096505462621628E-2</v>
       </c>
       <c r="E341">
         <v>217</v>
       </c>
       <c r="F341" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -8295,7 +8295,7 @@
         <v>217</v>
       </c>
       <c r="F342" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -8316,7 +8316,7 @@
         <v>217</v>
       </c>
       <c r="F343" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -8337,7 +8337,7 @@
         <v>217</v>
       </c>
       <c r="F344" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -8358,7 +8358,7 @@
         <v>217</v>
       </c>
       <c r="F345" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -8379,7 +8379,7 @@
         <v>217</v>
       </c>
       <c r="F346" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -8400,7 +8400,7 @@
         <v>217</v>
       </c>
       <c r="F347" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -8421,7 +8421,7 @@
         <v>217</v>
       </c>
       <c r="F348" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -8442,7 +8442,7 @@
         <v>217</v>
       </c>
       <c r="F349" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -8463,7 +8463,7 @@
         <v>217</v>
       </c>
       <c r="F350" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -8484,7 +8484,7 @@
         <v>217</v>
       </c>
       <c r="F351" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
@@ -8505,7 +8505,7 @@
         <v>217</v>
       </c>
       <c r="F352" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
@@ -8526,7 +8526,7 @@
         <v>217</v>
       </c>
       <c r="F353" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
@@ -8547,7 +8547,49 @@
         <v>217</v>
       </c>
       <c r="F354" t="s">
-        <v>129</v>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A355" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B355" s="2">
+        <v>2218.9580000000001</v>
+      </c>
+      <c r="C355">
+        <v>2212.31</v>
+      </c>
+      <c r="D355">
+        <f t="shared" si="16"/>
+        <v>0.30050038195371076</v>
+      </c>
+      <c r="E355">
+        <v>217</v>
+      </c>
+      <c r="F355" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A356" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B356" s="2">
+        <v>2247.77</v>
+      </c>
+      <c r="C356">
+        <v>2212.31</v>
+      </c>
+      <c r="D356">
+        <f t="shared" si="16"/>
+        <v>1.6028495102404292</v>
+      </c>
+      <c r="E356">
+        <v>217</v>
+      </c>
+      <c r="F356" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/Data/CRMAccuracyData.xlsx
+++ b/Data/CRMAccuracyData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Titrator\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D2C5D31-A81C-4CA6-B3C6-AFB3244975D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A253647-4D84-47AF-B357-9DFC74749718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13605" yWindow="690" windowWidth="14775" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="720" windowWidth="17145" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CRMAccuracyData" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="132">
   <si>
     <t>Date</t>
   </si>
@@ -425,7 +425,10 @@
     <t>same CRM opened 9/18/2026, MP ran at end of 62 samples</t>
   </si>
   <si>
-    <t>same CRM opened 9/18/2026 - testing Metrohm acid</t>
+    <t>new CRM opened 10/28/2026. using Metrohm titrant w/ concentration=0.101125</t>
+  </si>
+  <si>
+    <t>same CRM opened 10/28/2026</t>
   </si>
 </sst>
 </file>
@@ -8267,7 +8270,7 @@
         <v>2212.31</v>
       </c>
       <c r="D341">
-        <f t="shared" ref="D341:D356" si="16">100*(B341-C341)/C341</f>
+        <f t="shared" ref="D341:D355" si="16">100*(B341-C341)/C341</f>
         <v>-5.0096505462621628E-2</v>
       </c>
       <c r="E341">
@@ -8552,20 +8555,20 @@
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="1">
-        <v>46321</v>
-      </c>
-      <c r="B355" s="2">
-        <v>2218.9580000000001</v>
+        <v>46323</v>
+      </c>
+      <c r="B355">
+        <v>2208.2145607079701</v>
       </c>
       <c r="C355">
-        <v>2212.31</v>
+        <v>2210.1999999999998</v>
       </c>
       <c r="D355">
         <f t="shared" si="16"/>
-        <v>0.30050038195371076</v>
+        <v>-8.9830752512428558E-2</v>
       </c>
       <c r="E355">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="F355" t="s">
         <v>130</v>
@@ -8573,23 +8576,23 @@
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" s="1">
-        <v>46321</v>
-      </c>
-      <c r="B356" s="2">
-        <v>2247.77</v>
+        <v>46324</v>
+      </c>
+      <c r="B356">
+        <v>2208.9469234640601</v>
       </c>
       <c r="C356">
-        <v>2212.31</v>
+        <v>2210.1999999999998</v>
       </c>
       <c r="D356">
-        <f t="shared" si="16"/>
-        <v>1.6028495102404292</v>
+        <f t="shared" ref="D356" si="17">100*(B356-C356)/C356</f>
+        <v>-5.6695164959719782E-2</v>
       </c>
       <c r="E356">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="F356" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/Data/CRMAccuracyData.xlsx
+++ b/Data/CRMAccuracyData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Titrator\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A253647-4D84-47AF-B357-9DFC74749718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DC1504B-2E59-4A36-981D-8B2811E023A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="720" windowWidth="17145" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="720" windowWidth="17145" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CRMAccuracyData" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="132">
   <si>
     <t>Date</t>
   </si>
@@ -1294,7 +1294,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G356"/>
+  <dimension ref="A1:G357"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -8595,6 +8595,27 @@
         <v>131</v>
       </c>
     </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A357" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B357">
+        <v>2227.0935546189598</v>
+      </c>
+      <c r="C357">
+        <v>2210.1999999999998</v>
+      </c>
+      <c r="D357">
+        <f t="shared" ref="D357" si="18">100*(B357-C357)/C357</f>
+        <v>0.7643450646529738</v>
+      </c>
+      <c r="E357">
+        <v>227</v>
+      </c>
+      <c r="F357" t="s">
+        <v>131</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
